--- a/saidas/payroll-03.xlsx
+++ b/saidas/payroll-03.xlsx
@@ -39,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00173772"/>
+        <fgColor rgb="000B5D57"/>
       </patternFill>
     </fill>
   </fills>
